--- a/day_operations.xlsx
+++ b/day_operations.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="58">
   <si>
     <t>book title</t>
   </si>
@@ -31,82 +31,163 @@
     <t>to - date</t>
   </si>
   <si>
-    <t>space</t>
-  </si>
-  <si>
-    <t>None</t>
+    <t>Python Programming</t>
+  </si>
+  <si>
+    <t>Alice</t>
   </si>
   <si>
     <t>Retrieve</t>
   </si>
   <si>
-    <t>2019-01-08</t>
-  </si>
-  <si>
-    <t>python</t>
-  </si>
-  <si>
-    <t>mahmoud</t>
-  </si>
-  <si>
-    <t>2019-01-09</t>
-  </si>
-  <si>
-    <t>s</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>2019-01-10</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>h</t>
-  </si>
-  <si>
-    <t>2019-01-13</t>
-  </si>
-  <si>
-    <t>python OOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mahmoud </t>
-  </si>
-  <si>
-    <t>rent</t>
-  </si>
-  <si>
-    <t>2019-01-17</t>
-  </si>
-  <si>
-    <t>pyqt5</t>
-  </si>
-  <si>
-    <t>jack</t>
-  </si>
-  <si>
-    <t>2019-01-15</t>
-  </si>
-  <si>
-    <t>qtdesigner</t>
-  </si>
-  <si>
-    <t>ali</t>
-  </si>
-  <si>
-    <t>python basics</t>
-  </si>
-  <si>
-    <t>mahmoud ahmed</t>
-  </si>
-  <si>
-    <t>2019-01-16</t>
+    <t>2024-11-20</t>
+  </si>
+  <si>
+    <t>2024-11-25</t>
+  </si>
+  <si>
+    <t>Java Basics</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>2024-11-18</t>
+  </si>
+  <si>
+    <t>2024-11-21</t>
+  </si>
+  <si>
+    <t>The Great Adventure</t>
+  </si>
+  <si>
+    <t>Charlie</t>
+  </si>
+  <si>
+    <t>2024-11-19</t>
+  </si>
+  <si>
+    <t>2024-11-23</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>2024-11-17</t>
+  </si>
+  <si>
+    <t>2024-11-24</t>
+  </si>
+  <si>
+    <t>Deep Learning Explained</t>
+  </si>
+  <si>
+    <t>Eve</t>
+  </si>
+  <si>
+    <t>Rent</t>
+  </si>
+  <si>
+    <t>2024-11-16</t>
+  </si>
+  <si>
+    <t>2024-11-22</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>2024-11-15</t>
+  </si>
+  <si>
+    <t>Cooking with Love</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>2024-11-13</t>
+  </si>
+  <si>
+    <t>Sports and Fitness</t>
+  </si>
+  <si>
+    <t>Heidi</t>
+  </si>
+  <si>
+    <t>2024-11-12</t>
+  </si>
+  <si>
+    <t>Drama Unfolded</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>2024-11-10</t>
+  </si>
+  <si>
+    <t>2024-11-05</t>
+  </si>
+  <si>
+    <t>2024-11-07</t>
+  </si>
+  <si>
+    <t>Gaming Tricks</t>
+  </si>
+  <si>
+    <t>Judy</t>
+  </si>
+  <si>
+    <t>2024-11-11</t>
+  </si>
+  <si>
+    <t>Space Exploration</t>
+  </si>
+  <si>
+    <t>2024-11-06</t>
+  </si>
+  <si>
+    <t>2024-10-30</t>
+  </si>
+  <si>
+    <t>2024-10-28</t>
+  </si>
+  <si>
+    <t>2024-11-02</t>
+  </si>
+  <si>
+    <t>2024-10-25</t>
+  </si>
+  <si>
+    <t>Learn SQL</t>
+  </si>
+  <si>
+    <t>2024-10-20</t>
+  </si>
+  <si>
+    <t>2024-10-24</t>
+  </si>
+  <si>
+    <t>2024-10-10</t>
+  </si>
+  <si>
+    <t>2024-10-17</t>
+  </si>
+  <si>
+    <t>2024-10-15</t>
+  </si>
+  <si>
+    <t>2024-10-05</t>
+  </si>
+  <si>
+    <t>2024-10-14</t>
+  </si>
+  <si>
+    <t>2024-10-01</t>
+  </si>
+  <si>
+    <t>2024-10-06</t>
   </si>
 </sst>
 </file>
@@ -438,7 +519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -472,160 +553,330 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B15" t="s">
         <v>29</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="D11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
